--- a/shared/CallerID-Database.xlsx
+++ b/shared/CallerID-Database.xlsx
@@ -9,12 +9,12 @@
     <sheet sheetId="3" name="Numbers" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Files" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="149">
   <si>
     <t>packageId</t>
   </si>
@@ -184,6 +184,21 @@
     <t>2026-10-24T06:32:05.952Z</t>
   </si>
   <si>
+    <t>REQ-56b7b128</t>
+  </si>
+  <si>
+    <t>bank</t>
+  </si>
+  <si>
+    <t>always yours</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>2026-10-24T07:21:00.000Z</t>
+  </si>
+  <si>
     <t>numberId</t>
   </si>
   <si>
@@ -359,6 +374,21 @@
   </si>
   <si>
     <t>+63 1800 1012 3555</t>
+  </si>
+  <si>
+    <t>NUM-56b7b001</t>
+  </si>
+  <si>
+    <t>NUM-56b7b002</t>
+  </si>
+  <si>
+    <t>NUM-56b7b003</t>
+  </si>
+  <si>
+    <t>NUM-56b7b004</t>
+  </si>
+  <si>
+    <t>NUM-56b7b005</t>
   </si>
   <si>
     <t>fileId</t>
@@ -1303,7 +1333,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="14" customWidth="1"/>
@@ -1519,6 +1549,44 @@
       </c>
       <c r="M5" s="3" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>15000</v>
+      </c>
+      <c r="K6">
+        <v>1800</v>
+      </c>
+      <c r="L6">
+        <v>16800</v>
       </c>
     </row>
   </sheetData>
@@ -1536,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="14" customWidth="1"/>
@@ -1546,7 +1614,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>22</v>
@@ -1555,16 +1623,16 @@
         <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -1575,7 +1643,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
@@ -1584,16 +1652,16 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
         <v>35</v>
@@ -1604,7 +1672,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
@@ -1613,16 +1681,16 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
         <v>35</v>
@@ -1633,7 +1701,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
@@ -1642,16 +1710,16 @@
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
         <v>35</v>
@@ -1662,7 +1730,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
@@ -1671,16 +1739,16 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
         <v>35</v>
@@ -1691,7 +1759,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
@@ -1700,16 +1768,16 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s">
         <v>35</v>
@@ -1720,7 +1788,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
@@ -1729,16 +1797,16 @@
         <v>41</v>
       </c>
       <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" t="s">
         <v>70</v>
-      </c>
-      <c r="E7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" t="s">
-        <v>65</v>
       </c>
       <c r="H7" t="s">
         <v>43</v>
@@ -1749,7 +1817,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
@@ -1758,16 +1826,16 @@
         <v>41</v>
       </c>
       <c r="D8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" t="s">
         <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
       </c>
       <c r="H8" t="s">
         <v>43</v>
@@ -1778,7 +1846,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -1787,16 +1855,16 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s">
         <v>43</v>
@@ -1807,7 +1875,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
@@ -1816,16 +1884,16 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
         <v>43</v>
@@ -1836,7 +1904,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
         <v>47</v>
@@ -1845,16 +1913,16 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H11" t="s">
         <v>43</v>
@@ -1865,7 +1933,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
@@ -1874,16 +1942,16 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
         <v>43</v>
@@ -1894,7 +1962,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
@@ -1903,16 +1971,16 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
         <v>43</v>
@@ -1923,7 +1991,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
         <v>47</v>
@@ -1932,16 +2000,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>43</v>
@@ -1952,7 +2020,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -1961,16 +2029,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
         <v>43</v>
@@ -1981,7 +2049,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B16" t="s">
         <v>52</v>
@@ -1990,16 +2058,16 @@
         <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
         <v>35</v>
@@ -2010,7 +2078,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s">
         <v>52</v>
@@ -2019,16 +2087,16 @@
         <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>35</v>
@@ -2039,7 +2107,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s">
         <v>52</v>
@@ -2048,16 +2116,16 @@
         <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s">
         <v>35</v>
@@ -2068,7 +2136,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
         <v>52</v>
@@ -2077,16 +2145,16 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H19" t="s">
         <v>35</v>
@@ -2097,7 +2165,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
         <v>52</v>
@@ -2106,22 +2174,167 @@
         <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
       </c>
       <c r="I20" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2144,37 +2357,37 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>31</v>
@@ -2188,28 +2401,28 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H2">
         <v>869308</v>
       </c>
       <c r="I2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="J2" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K2" t="s">
         <v>37</v>
@@ -2223,28 +2436,28 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H3">
         <v>869308</v>
       </c>
       <c r="I3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="J3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K3" t="s">
         <v>45</v>
@@ -2258,28 +2471,28 @@
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H4">
         <v>12539</v>
       </c>
       <c r="I4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="J4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K4" t="s">
         <v>51</v>
@@ -2293,28 +2506,28 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H5">
         <v>869308</v>
       </c>
       <c r="I5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="J5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K5" t="s">
         <v>55</v>
